--- a/ValueSet-ACCESSeCKMDiagnosisVS.xlsx
+++ b/ValueSet-ACCESSeCKMDiagnosisVS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T23:16:42-05:00</t>
+    <t>2026-03-06T16:03:26-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ACCESSeCKMDiagnosisVS.xlsx
+++ b/ValueSet-ACCESSeCKMDiagnosisVS.xlsx
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://globalalliantinc.com/access/ValueSet/ACCESSeCKMDiagnosisVS</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSeCKMDiagnosisVS</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T16:03:26-05:00</t>
+    <t>2026-03-12T23:55:37-07:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ACCESSeCKMDiagnosisVS.xlsx
+++ b/ValueSet-ACCESSeCKMDiagnosisVS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.1</t>
+    <t>0.9.6</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T23:55:37-07:00</t>
+    <t>2026-04-24T13:45:33-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ACCESSeCKMDiagnosisVS.xlsx
+++ b/ValueSet-ACCESSeCKMDiagnosisVS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.6</t>
+    <t>0.9.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:45:33-04:00</t>
+    <t>2026-05-18T15:59:44-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ACCESSeCKMDiagnosisVS.xlsx
+++ b/ValueSet-ACCESSeCKMDiagnosisVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T15:59:44-04:00</t>
+    <t>2026-05-20T09:30:43-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ACCESSeCKMDiagnosisVS.xlsx
+++ b/ValueSet-ACCESSeCKMDiagnosisVS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="163">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.8</t>
+    <t>0.9.11</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-20T09:30:43-04:00</t>
+    <t>2026-06-04T22:54:52-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,6 +105,174 @@
     <t>Concept</t>
   </si>
   <si>
+    <t>E66.01</t>
+  </si>
+  <si>
+    <t>Morbid (severe) obesity due to excess calories</t>
+  </si>
+  <si>
+    <t>E66.09</t>
+  </si>
+  <si>
+    <t>Other obesity due to excess calories</t>
+  </si>
+  <si>
+    <t>E66.1</t>
+  </si>
+  <si>
+    <t>Drug-induced obesity</t>
+  </si>
+  <si>
+    <t>E66.2</t>
+  </si>
+  <si>
+    <t>Morbid (severe) obesity with alveolar hypoventilation</t>
+  </si>
+  <si>
+    <t>E66.3</t>
+  </si>
+  <si>
+    <t>Overweight</t>
+  </si>
+  <si>
+    <t>E66.811</t>
+  </si>
+  <si>
+    <t>Obesity, class 1</t>
+  </si>
+  <si>
+    <t>E66.812</t>
+  </si>
+  <si>
+    <t>Obesity, class 2</t>
+  </si>
+  <si>
+    <t>E66.813</t>
+  </si>
+  <si>
+    <t>Obesity, class 3</t>
+  </si>
+  <si>
+    <t>E66.89</t>
+  </si>
+  <si>
+    <t>Other obesity not elsewhere classified</t>
+  </si>
+  <si>
+    <t>E66.9</t>
+  </si>
+  <si>
+    <t>Obesity, unspecified</t>
+  </si>
+  <si>
+    <t>E78.00</t>
+  </si>
+  <si>
+    <t>Pure hypercholesterolemia, unspecified</t>
+  </si>
+  <si>
+    <t>E78.010</t>
+  </si>
+  <si>
+    <t>Homozygous familial hypercholesterolemia [HoFH]</t>
+  </si>
+  <si>
+    <t>E78.011</t>
+  </si>
+  <si>
+    <t>Heterozygous familial hypercholesterolemia [HeFH]</t>
+  </si>
+  <si>
+    <t>E78.019</t>
+  </si>
+  <si>
+    <t>Familial hypercholesterolemia, unspecified</t>
+  </si>
+  <si>
+    <t>E78.1</t>
+  </si>
+  <si>
+    <t>Pure hyperglyceridemia</t>
+  </si>
+  <si>
+    <t>E78.2</t>
+  </si>
+  <si>
+    <t>Mixed hyperlipidemia</t>
+  </si>
+  <si>
+    <t>E78.3</t>
+  </si>
+  <si>
+    <t>Hyperchylomicronemia</t>
+  </si>
+  <si>
+    <t>E78.41</t>
+  </si>
+  <si>
+    <t>Elevated Lipoprotein(a)</t>
+  </si>
+  <si>
+    <t>E78.49</t>
+  </si>
+  <si>
+    <t>Other hyperlipidemia</t>
+  </si>
+  <si>
+    <t>E78.5</t>
+  </si>
+  <si>
+    <t>Hyperlipidemia, unspecified</t>
+  </si>
+  <si>
+    <t>E78.6</t>
+  </si>
+  <si>
+    <t>Lipoprotein deficiency</t>
+  </si>
+  <si>
+    <t>E78.70</t>
+  </si>
+  <si>
+    <t>Disorder of bile acid and cholesterol metabolism, unspecified</t>
+  </si>
+  <si>
+    <t>E78.71</t>
+  </si>
+  <si>
+    <t>Barth syndrome</t>
+  </si>
+  <si>
+    <t>E78.72</t>
+  </si>
+  <si>
+    <t>Smith-Lemli-Opitz syndrome</t>
+  </si>
+  <si>
+    <t>E78.79</t>
+  </si>
+  <si>
+    <t>Other disorders of bile acid and cholesterol metabolism</t>
+  </si>
+  <si>
+    <t>E78.81</t>
+  </si>
+  <si>
+    <t>Lipoid dermatoarthritis</t>
+  </si>
+  <si>
+    <t>E78.89</t>
+  </si>
+  <si>
+    <t>Other lipoprotein metabolism disorders</t>
+  </si>
+  <si>
+    <t>E78.9</t>
+  </si>
+  <si>
+    <t>Disorder of lipoprotein metabolism, unspecified</t>
+  </si>
+  <si>
     <t>I10</t>
   </si>
   <si>
@@ -123,6 +291,12 @@
     <t>Hypertensive heart disease without heart failure</t>
   </si>
   <si>
+    <t>I12.0</t>
+  </si>
+  <si>
+    <t>Hypertensive chronic kidney disease with stage 5 chronic kidney disease or end stage renal disease</t>
+  </si>
+  <si>
     <t>I12.9</t>
   </si>
   <si>
@@ -147,6 +321,12 @@
     <t>Hypertensive heart and chronic kidney disease without heart failure, with stage 5 chronic kidney disease, or end stage renal disease</t>
   </si>
   <si>
+    <t>I13.2</t>
+  </si>
+  <si>
+    <t>Hypertensive heart and chronic kidney disease with heart failure and with stage 5 chronic kidney disease, or end stage renal disease</t>
+  </si>
+  <si>
     <t>I15.0</t>
   </si>
   <si>
@@ -183,79 +363,118 @@
     <t>Resistant hypertension</t>
   </si>
   <si>
+    <t>I67.0</t>
+  </si>
+  <si>
+    <t>Dissection of cerebral arteries, nonruptured</t>
+  </si>
+  <si>
+    <t>I67.1</t>
+  </si>
+  <si>
+    <t>Cerebral aneurysm, nonruptured</t>
+  </si>
+  <si>
+    <t>I67.2</t>
+  </si>
+  <si>
+    <t>Cerebral atherosclerosis</t>
+  </si>
+  <si>
+    <t>I67.3</t>
+  </si>
+  <si>
+    <t>Progressive vascular leukoencephalopathy</t>
+  </si>
+  <si>
     <t>I67.4</t>
   </si>
   <si>
     <t>Hypertensive encephalopathy</t>
   </si>
   <si>
-    <t>E78.0</t>
-  </si>
-  <si>
-    <t>Pure hypercholesterolemia</t>
-  </si>
-  <si>
-    <t>E78.00</t>
-  </si>
-  <si>
-    <t>Pure hypercholesterolemia, unspecified</t>
-  </si>
-  <si>
-    <t>E78.01</t>
-  </si>
-  <si>
-    <t>Familial hypercholesterolemia</t>
-  </si>
-  <si>
-    <t>E78.1</t>
-  </si>
-  <si>
-    <t>Pure hyperglyceridemia</t>
-  </si>
-  <si>
-    <t>E78.2</t>
-  </si>
-  <si>
-    <t>Mixed hyperlipidemia</t>
-  </si>
-  <si>
-    <t>E78.3</t>
-  </si>
-  <si>
-    <t>Hyperchylomicronemia</t>
-  </si>
-  <si>
-    <t>E78.4</t>
-  </si>
-  <si>
-    <t>Other hyperlipidemia</t>
-  </si>
-  <si>
-    <t>E78.41</t>
-  </si>
-  <si>
-    <t>Elevated lipoprotein(a)</t>
-  </si>
-  <si>
-    <t>E78.49</t>
-  </si>
-  <si>
-    <t>E78.5</t>
-  </si>
-  <si>
-    <t>Hyperlipidemia, unspecified</t>
-  </si>
-  <si>
-    <t>E78.6</t>
-  </si>
-  <si>
-    <t>Lipoprotein deficiency</t>
-  </si>
-  <si>
-    <t>E78.7</t>
-  </si>
-  <si>
-    <t>Disorders of bile acid and cholesterol metabolism</t>
+    <t>I67.5</t>
+  </si>
+  <si>
+    <t>Moyamoya disease</t>
+  </si>
+  <si>
+    <t>I67.6</t>
+  </si>
+  <si>
+    <t>Nonpyogenic thrombosis of intracranial venous system</t>
+  </si>
+  <si>
+    <t>I67.7</t>
+  </si>
+  <si>
+    <t>Cerebral arteritis, not elsewhere classified</t>
+  </si>
+  <si>
+    <t>I67.81</t>
+  </si>
+  <si>
+    <t>Acute cerebrovascular insufficiency</t>
+  </si>
+  <si>
+    <t>I67.82</t>
+  </si>
+  <si>
+    <t>Cerebral ischemia</t>
+  </si>
+  <si>
+    <t>I67.83</t>
+  </si>
+  <si>
+    <t>Posterior reversible encephalopathy syndrome</t>
+  </si>
+  <si>
+    <t>I67.841</t>
+  </si>
+  <si>
+    <t>Reversible cerebrovascular vasoconstriction syndrome</t>
+  </si>
+  <si>
+    <t>I67.848</t>
+  </si>
+  <si>
+    <t>Other cerebrovascular vasospasm and vasoconstriction</t>
+  </si>
+  <si>
+    <t>I67.850</t>
+  </si>
+  <si>
+    <t>Cerebral autosomal dominant arteriopathy with subcortical infarcts and leukoencephalopathy</t>
+  </si>
+  <si>
+    <t>I67.858</t>
+  </si>
+  <si>
+    <t>Other hereditary cerebrovascular disease</t>
+  </si>
+  <si>
+    <t>I67.89</t>
+  </si>
+  <si>
+    <t>Other cerebrovascular disease</t>
+  </si>
+  <si>
+    <t>I67.9</t>
+  </si>
+  <si>
+    <t>Cerebrovascular disease, unspecified</t>
+  </si>
+  <si>
+    <t>R73.01</t>
+  </si>
+  <si>
+    <t>Impaired fasting glucose</t>
+  </si>
+  <si>
+    <t>R73.02</t>
+  </si>
+  <si>
+    <t>Impaired glucose tolerance (oral)</t>
   </si>
   <si>
     <t>R73.03</t>
@@ -264,46 +483,16 @@
     <t>Prediabetes</t>
   </si>
   <si>
-    <t>E66.01</t>
-  </si>
-  <si>
-    <t>Morbid (severe) obesity due to excess calories</t>
-  </si>
-  <si>
-    <t>E66.09</t>
-  </si>
-  <si>
-    <t>Other obesity due to excess calories</t>
-  </si>
-  <si>
-    <t>E66.1</t>
-  </si>
-  <si>
-    <t>Drug-induced obesity</t>
-  </si>
-  <si>
-    <t>E66.2</t>
-  </si>
-  <si>
-    <t>Morbid (severe) obesity with alveolar hypoventilation</t>
-  </si>
-  <si>
-    <t>E66.3</t>
-  </si>
-  <si>
-    <t>Overweight</t>
-  </si>
-  <si>
-    <t>E66.8</t>
-  </si>
-  <si>
-    <t>Other obesity</t>
-  </si>
-  <si>
-    <t>E66.9</t>
-  </si>
-  <si>
-    <t>Obesity, unspecified</t>
+    <t>R73.09</t>
+  </si>
+  <si>
+    <t>Other abnormal glucose</t>
+  </si>
+  <si>
+    <t>R73.9</t>
+  </si>
+  <si>
+    <t>Hyperglycemia, unspecified</t>
   </si>
   <si>
     <t/>
@@ -578,7 +767,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B68"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -774,111 +963,359 @@
         <v>74</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-ACCESSeCKMDiagnosisVS.xlsx
+++ b/ValueSet-ACCESSeCKMDiagnosisVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T22:54:52-04:00</t>
+    <t>2026-06-04T23:05:21-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ACCESSeCKMDiagnosisVS.xlsx
+++ b/ValueSet-ACCESSeCKMDiagnosisVS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="123">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.11</t>
+    <t>0.9.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T23:05:21-04:00</t>
+    <t>2026-06-10T23:08:55-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -291,12 +291,6 @@
     <t>Hypertensive heart disease without heart failure</t>
   </si>
   <si>
-    <t>I12.0</t>
-  </si>
-  <si>
-    <t>Hypertensive chronic kidney disease with stage 5 chronic kidney disease or end stage renal disease</t>
-  </si>
-  <si>
     <t>I12.9</t>
   </si>
   <si>
@@ -315,18 +309,6 @@
     <t>Hypertensive heart and chronic kidney disease without heart failure, with stage 1 through stage 4 chronic kidney disease, or unspecified chronic kidney disease</t>
   </si>
   <si>
-    <t>I13.11</t>
-  </si>
-  <si>
-    <t>Hypertensive heart and chronic kidney disease without heart failure, with stage 5 chronic kidney disease, or end stage renal disease</t>
-  </si>
-  <si>
-    <t>I13.2</t>
-  </si>
-  <si>
-    <t>Hypertensive heart and chronic kidney disease with heart failure and with stage 5 chronic kidney disease, or end stage renal disease</t>
-  </si>
-  <si>
     <t>I15.0</t>
   </si>
   <si>
@@ -361,108 +343,6 @@
   </si>
   <si>
     <t>Resistant hypertension</t>
-  </si>
-  <si>
-    <t>I67.0</t>
-  </si>
-  <si>
-    <t>Dissection of cerebral arteries, nonruptured</t>
-  </si>
-  <si>
-    <t>I67.1</t>
-  </si>
-  <si>
-    <t>Cerebral aneurysm, nonruptured</t>
-  </si>
-  <si>
-    <t>I67.2</t>
-  </si>
-  <si>
-    <t>Cerebral atherosclerosis</t>
-  </si>
-  <si>
-    <t>I67.3</t>
-  </si>
-  <si>
-    <t>Progressive vascular leukoencephalopathy</t>
-  </si>
-  <si>
-    <t>I67.4</t>
-  </si>
-  <si>
-    <t>Hypertensive encephalopathy</t>
-  </si>
-  <si>
-    <t>I67.5</t>
-  </si>
-  <si>
-    <t>Moyamoya disease</t>
-  </si>
-  <si>
-    <t>I67.6</t>
-  </si>
-  <si>
-    <t>Nonpyogenic thrombosis of intracranial venous system</t>
-  </si>
-  <si>
-    <t>I67.7</t>
-  </si>
-  <si>
-    <t>Cerebral arteritis, not elsewhere classified</t>
-  </si>
-  <si>
-    <t>I67.81</t>
-  </si>
-  <si>
-    <t>Acute cerebrovascular insufficiency</t>
-  </si>
-  <si>
-    <t>I67.82</t>
-  </si>
-  <si>
-    <t>Cerebral ischemia</t>
-  </si>
-  <si>
-    <t>I67.83</t>
-  </si>
-  <si>
-    <t>Posterior reversible encephalopathy syndrome</t>
-  </si>
-  <si>
-    <t>I67.841</t>
-  </si>
-  <si>
-    <t>Reversible cerebrovascular vasoconstriction syndrome</t>
-  </si>
-  <si>
-    <t>I67.848</t>
-  </si>
-  <si>
-    <t>Other cerebrovascular vasospasm and vasoconstriction</t>
-  </si>
-  <si>
-    <t>I67.850</t>
-  </si>
-  <si>
-    <t>Cerebral autosomal dominant arteriopathy with subcortical infarcts and leukoencephalopathy</t>
-  </si>
-  <si>
-    <t>I67.858</t>
-  </si>
-  <si>
-    <t>Other hereditary cerebrovascular disease</t>
-  </si>
-  <si>
-    <t>I67.89</t>
-  </si>
-  <si>
-    <t>Other cerebrovascular disease</t>
-  </si>
-  <si>
-    <t>I67.9</t>
-  </si>
-  <si>
-    <t>Cerebrovascular disease, unspecified</t>
   </si>
   <si>
     <t>R73.01</t>
@@ -767,7 +647,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B68"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1147,175 +1027,15 @@
         <v>120</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="B48" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>162</v>
       </c>
     </row>
   </sheetData>
